--- a/reports/scan/fs_fintech_fs.xlsx
+++ b/reports/scan/fs_fintech_fs.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -622,9 +622,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -637,9 +637,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -714,9 +714,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -791,9 +791,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -917,62 +917,62 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1022,9 +1022,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1069,74 +1069,74 @@
           <t>security/audit/access_log.txt</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1196,9 +1196,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1238,26 +1238,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1273,9 +1273,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1330,9 +1330,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1581,9 +1581,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1658,9 +1658,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1779,57 +1779,57 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
@@ -1889,9 +1889,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1938,14 +1938,14 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
           <t>12</t>
         </is>
       </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1966,9 +1966,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2013,39 +2013,39 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2120,9 +2120,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2197,9 +2197,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2274,9 +2274,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">

--- a/reports/scan/fs_fintech_fs.xlsx
+++ b/reports/scan/fs_fintech_fs.xlsx
@@ -532,72 +532,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -609,72 +609,72 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -917,62 +917,62 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1007,9 +1007,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1084,9 +1084,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1148,72 +1148,72 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1225,72 +1225,72 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1397,9 +1397,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1474,9 +1474,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1551,9 +1551,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1608,9 +1608,9 @@
           <t>customers/cust_0001/</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1628,49 +1628,49 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1705,49 +1705,49 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1779,47 +1779,47 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1889,9 +1889,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1941,44 +1941,44 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2120,9 +2120,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -2224,74 +2224,74 @@
           <t>source/</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>limits output to last N lines, but large values can still be risky</t>
+          <t>limits output to last N lines, but large values can still be problematic</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>limits output to first N lines, but large values can still be risky</t>
+          <t>limits output to first N lines, but large values can still be problematic</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>limits output to last N lines, but large values can still be problematic</t>
+          <t>limits output to last N lines, but large values can be resource-intensive</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>limits output to first N lines, but large values can still be problematic</t>
+          <t>limits output to first N lines, but large values can be resource-intensive</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>can be used to create directories in sensitive locations</t>
+          <t>can be used to create arbitrary directory paths</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>can point to sensitive directories</t>
+          <t>Can target any directory, potentially exposing sensitive information</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>only affects sorting, not scope or action</t>
+          <t>Limited to predefined sorting options, no amplification of risk</t>
         </is>
       </c>
     </row>

--- a/reports/scan/fs_fintech_fs.xlsx
+++ b/reports/scan/fs_fintech_fs.xlsx
@@ -932,12 +932,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1166,9 +1166,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1230,57 +1230,57 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1591,9 +1591,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1745,9 +1745,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1889,9 +1889,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1941,9 +1941,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2169,37 +2169,37 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2246,47 +2246,47 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
